--- a/projects/wanos-board/components.xlsx
+++ b/projects/wanos-board/components.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.28515625" defaultRowHeight="15"/>
   <cols>
     <col width="12.85546875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -515,6 +515,11 @@
           <t>MountType</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -575,6 +580,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,6 +645,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -695,6 +710,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -755,6 +775,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -815,6 +840,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -875,6 +905,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -935,6 +970,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -995,6 +1035,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1055,6 +1100,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1115,6 +1165,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1175,6 +1230,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1235,6 +1295,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1295,6 +1360,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1355,6 +1425,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1415,6 +1490,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1475,6 +1555,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1535,6 +1620,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1595,6 +1685,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1655,6 +1750,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1715,6 +1815,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1775,6 +1880,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1835,6 +1945,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1895,6 +2010,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1955,6 +2075,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2015,6 +2140,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2075,6 +2205,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2135,6 +2270,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2195,6 +2335,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2255,6 +2400,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2315,6 +2465,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2375,6 +2530,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2435,6 +2595,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2495,6 +2660,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2555,6 +2725,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2615,6 +2790,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2675,6 +2855,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2735,6 +2920,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2795,6 +2985,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2855,6 +3050,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2915,6 +3115,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2975,6 +3180,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3035,6 +3245,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3095,6 +3310,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3155,6 +3375,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3210,6 +3435,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3270,6 +3500,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3330,6 +3565,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3390,6 +3630,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3450,6 +3695,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3510,6 +3760,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3570,6 +3825,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3620,6 +3880,11 @@
           <t>TH</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3680,6 +3945,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3740,6 +4010,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3800,6 +4075,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3860,6 +4140,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3920,6 +4205,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3975,6 +4265,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4030,6 +4325,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4085,6 +4385,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4140,6 +4445,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4195,6 +4505,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4250,6 +4565,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4305,6 +4625,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4360,6 +4685,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4415,6 +4745,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4470,6 +4805,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4525,6 +4865,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4580,6 +4925,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4635,6 +4985,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4690,6 +5045,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4745,6 +5105,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4800,6 +5165,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4855,6 +5225,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4910,6 +5285,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4965,6 +5345,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5020,6 +5405,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5075,6 +5465,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5130,6 +5525,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5185,6 +5585,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5240,6 +5645,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5295,6 +5705,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5350,6 +5765,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5405,6 +5825,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5460,6 +5885,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5515,6 +5945,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5570,6 +6005,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5625,6 +6065,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5680,6 +6125,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5735,6 +6185,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5790,6 +6245,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5840,6 +6300,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5895,6 +6360,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5950,6 +6420,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6005,6 +6480,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6060,6 +6540,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6115,6 +6600,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6170,6 +6660,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6225,6 +6720,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6285,6 +6785,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6345,6 +6850,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6405,6 +6915,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6465,6 +6980,11 @@
           <t>SMT</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6523,6 +7043,4311 @@
       <c r="L105" t="inlineStr">
         <is>
           <t>SMT</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Connector_RJ:RJ45_Amphenol_54602-x08_Horizontal</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>5556416-1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>C86492</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Uplink Cat5 to main U5 mux; TE no-LED no-magnetics; pair map remotepcb.md §5</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>RJ45</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Universal pulse pulse ch1; pin1 S0_RAIL, pin2 SIG, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Universal pulse pulse ch2; pin1 S0_RAIL, pin2 SIG, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Universal pulse pulse ch3; pin1 S0_RAIL, pin2 SIG, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Universal pulse pulse ch4; pin1 S0_RAIL, pin2 SIG, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>DS18B20 temp ch1; pin1 +3V3, pin2 1-Wire, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>DS18B20 temp ch2; pin1 +3V3, pin2 1-Wire, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>DS18B20 temp ch3; pin1 +3V3, pin2 1-Wire, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>JST XH 3-pin</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Connector_JST:JST_XH_B3B-XH-A_1x03_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>B3B-XH-A</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>C157925</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>DS18B20 temp ch4; pin1 +3V3, pin2 1-Wire, pin3 GND</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>XH-3</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>TLP281-4</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Package_SO:SOIC-16_3.9x9.9mm_P1.27mm</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>TLP281-4(GB-TP,J)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>C20525</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Optocoupler</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Quad opto field pulse isolation</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>SOIC-16</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>DS2482-800</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DS2482-800+</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>8-ch 1-Wire master I2C 0x18 (AD tied low); LCSC TBD - verify stock</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>TSSOP-16</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>MCP23017A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Package_SO:SOIC-28_7.5x17.9mm_P1.27mm</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MCP23017A-E/SO</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>C112159</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>I/O expander I2C 0x22; INT NC; A die required</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>SOIC-28</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AP2204K-3.3</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23-5</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>AP2204K-3.3TRG1</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>C82942</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>LDO VIN(~12V)-&gt;3V3; EN to VIN</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SW1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SPST tactile</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Button_Switch_SMD:SW_SPST_PTS645</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>PTS645S43SMTR92LFS</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>C139215</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Gates activity-LED anode rail only</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>C23179</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>R_IN pulse ch1 opto collector to MCP</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>C23179</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>R_IN pulse ch2 opto collector to MCP</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>C23179</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>R_IN pulse ch3 opto collector to MCP</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>C23179</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>R_IN pulse ch4 opto collector to MCP</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>C22962</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>R_PU PULSE_CH1 to +3V3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>C22962</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>R_PU PULSE_CH2 to +3V3</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>C22962</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>R_PU PULSE_CH3 to +3V3</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>C22962</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>R_PU PULSE_CH4 to +3V3</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>4k7</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0603WAF4701T5E</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>C23162</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>R_LED S0_RAIL to TLP281 ch1 anode (~2.3mA @12V)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>4k7</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0603WAF4701T5E</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>C23162</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>R_LED S0_RAIL to TLP281 ch2 anode (~2.3mA @12V)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4k7</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0603WAF4701T5E</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>C23162</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>R_LED S0_RAIL to TLP281 ch3 anode (~2.3mA @12V)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>4k7</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0603WAF4701T5E</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>C23162</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>R_LED S0_RAIL to TLP281 ch4 anode (~2.3mA @12V)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>C21190</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Activity LED series ch1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>C21190</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Activity LED series ch2</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>C21190</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Activity LED series ch3</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>C21190</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Activity LED series ch4</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>10R</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0603WAF100JT5E</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>C25804</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>R_S0 VIN to S0_RAIL</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>6k8</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0603WAF6801T5E</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>C23216</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Power LED series from S0_RAIL (match main R30 class)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>22R</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0603WAF220JT5E</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>C23206</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>I2C SDA series at remote</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>22R</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0603WAF220JT5E</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>C23206</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>I2C SCL series at remote</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2k2</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>C22940</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1-Wire pull-up ch1 to +3V3 at DS2482</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2k2</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>C22940</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1-Wire pull-up ch2 to +3V3 at DS2482</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2k2</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>C22940</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1-Wire pull-up ch3 to +3V3 at DS2482</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2k2</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>C22940</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1-Wire pull-up ch4 to +3V3 at DS2482</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>C_RC debounce PULSE_CH1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>C_RC debounce PULSE_CH2</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>C_RC debounce PULSE_CH3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>C_RC debounce PULSE_CH4</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>10u</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CL10A106KA8NNNC</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>C15850</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>C_S0 bulk on S0_RAIL (prefer &gt;=25V rating)</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>C_S0 HF on S0_RAIL</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>100u</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:CP_Elec_6.3x5.4mm</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>RVT1C101M0605</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>C72473</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LDO Cin electrolytic on VIN (16V class)</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>6.3x5.4</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>LDO Cin ceramic on VIN</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>47u</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>CL10A476MQ8NNNC</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>C15907</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>3V3 bulk near LDO out / IC cluster</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>10u</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>CL10A106KA8NNNC</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>C15850</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>3V3 bulk near DS2482/MCP cluster</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Decouple U2 DS2482 VCC</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Decouple U3 MCP23017A VCC</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Decouple U4 AP2204 output / local</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>100n</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Decouple logic HF near opto/MCP</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-323</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>C2927587</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ESD PULSE_CH1 to GND (logic side)</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>SOD-323</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-323</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>C2927587</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ESD PULSE_CH2 to GND (logic side)</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>SOD-323</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-323</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>C2927587</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ESD PULSE_CH3 to GND (logic side)</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>SOD-323</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-323</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ESD5B5.0ST5G</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>C2927587</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ESD PULSE_CH4 to GND (logic side)</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>SOD-323</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LED_SMD:LED_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>C2297</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Activity pulse ch1; gated by SW1</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LED_SMD:LED_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>C2297</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Activity pulse ch2; gated by SW1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LED_SMD:LED_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>C2297</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Activity pulse ch3; gated by SW1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LED_SMD:LED_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>C2297</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Activity pulse ch4; gated by SW1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LED_SMD:LED_0603_1608Metric</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>C2297</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Power present on S0_RAIL; always on with R18</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MH1</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>mountinghole</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>MountingHole</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>MountingHole:MountingHole_3.2mm_M3</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>MH3.2</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Mounting hole; copper clearance</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>3.2mm</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MH2</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>mountinghole</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>MountingHole</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>MountingHole:MountingHole_3.2mm_M3</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>MH3.2</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Mounting hole; copper clearance</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>3.2mm</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MH3</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>mountinghole</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>MountingHole</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>MountingHole:MountingHole_3.2mm_M3</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>MH3.2</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Mounting hole; copper clearance</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>3.2mm</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MH4</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>mountinghole</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>MountingHole</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>MountingHole:MountingHole_3.2mm_M3</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>MH3.2</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Mounting hole; copper clearance</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>3.2mm</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>SMBJ12A</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SMB</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>SMBJ12A</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>C353398</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>VIN to GND TVS at remote RJ45</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2u2</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>CL10A225KA8NNNC</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>C15808</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Capacitor</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>LDO VOUT ceramic &gt;=2.2uF</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>remote</t>
         </is>
       </c>
     </row>
